--- a/artfynd/A 22440-2026 artfynd.xlsx
+++ b/artfynd/A 22440-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133931370</v>
+        <v>133931265</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621423</v>
+        <v>621391</v>
       </c>
       <c r="R2" t="n">
-        <v>6649473</v>
+        <v>6649511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,10 +773,213 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133931370</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Runt Uppsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>621423</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6649473</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Annika Leers, Ki Mähler, Natt Söderpil Jakauby</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133931407</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Runt Uppsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>621467</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6649439</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Leers, Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22440-2026 artfynd.xlsx
+++ b/artfynd/A 22440-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,49 +780,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133931370</v>
+        <v>134680217</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Runt Uppsalaberget, Upl</t>
+          <t>Uppsalaberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621423</v>
+        <v>621452</v>
       </c>
       <c r="R3" t="n">
-        <v>6649473</v>
+        <v>6649489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,39 +851,50 @@
           <t>2026-05-28</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Francis Rogers</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler, Natt Söderpil Jakauby</t>
+          <t>Francis Rogers, Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133931407</v>
+        <v>133931370</v>
       </c>
       <c r="B4" t="n">
-        <v>98060</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,27 +902,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -920,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621467</v>
+        <v>621423</v>
       </c>
       <c r="R4" t="n">
-        <v>6649439</v>
+        <v>6649473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +974,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,10 +985,584 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Annika Leers, Ki Mähler, Natt Söderpil Jakauby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134680214</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Upsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>621384</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6649510</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår, gammalt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Francis Rogers</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Francis Rogers, Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134680215</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Uppsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>621384</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6649475</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår, äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Francis Rogers</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Francis Rogers, Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134680153</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Uppsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>621452</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6649489</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Francis Rogers</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Francis Rogers, Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134680212</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Uppsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>621465</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6649484</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Francis Rogers</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Francis Rogers, Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133931407</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Runt Uppsalaberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621467</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6649439</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Annika Leers, Ki Mähler</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22440-2026 artfynd.xlsx
+++ b/artfynd/A 22440-2026 artfynd.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Francis Rogers, Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Francis Rogers</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 22440-2026 artfynd.xlsx
+++ b/artfynd/A 22440-2026 artfynd.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Francis Rogers</t>
+          <t>Francis Rogers, Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
